--- a/data/trans_dic/P43B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P43B-Clase-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,74; 44,67</t>
+          <t>27,23; 45,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,77; 38,54</t>
+          <t>23,46; 38,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,22; 50,28</t>
+          <t>39,14; 50,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,74; 44,67</t>
+          <t>27,23; 45,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,77; 38,54</t>
+          <t>23,46; 38,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,22; 50,28</t>
+          <t>39,14; 50,42</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,05; 46,56</t>
+          <t>26,21; 46,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,05; 33,89</t>
+          <t>20,21; 34,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,83; 42,15</t>
+          <t>29,39; 41,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,05; 46,56</t>
+          <t>26,21; 46,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,05; 33,89</t>
+          <t>20,21; 34,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,83; 42,15</t>
+          <t>29,39; 41,29</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 24,39</t>
+          <t>10,39; 23,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 22,49</t>
+          <t>8,82; 24,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 23,12</t>
+          <t>9,51; 21,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 24,39</t>
+          <t>10,39; 23,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 22,49</t>
+          <t>8,82; 24,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 23,12</t>
+          <t>9,51; 21,78</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 18,92</t>
+          <t>10,4; 18,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 13,86</t>
+          <t>7,0; 14,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,36</t>
+          <t>10,73; 17,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 18,92</t>
+          <t>10,4; 18,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 13,86</t>
+          <t>7,0; 14,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,36</t>
+          <t>10,73; 17,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -955,39 +955,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,75</t>
+          <t>5,74; 11,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,15</t>
+          <t>2,87; 7,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,24</t>
+          <t>4,32; 9,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,75</t>
+          <t>5,74; 11,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,15</t>
+          <t>2,87; 7,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,24</t>
+          <t>4,32; 9,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,64</t>
+          <t>5,81; 11,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,69</t>
+          <t>6,53; 11,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,1</t>
+          <t>6,01; 11,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,64</t>
+          <t>5,81; 11,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,69</t>
+          <t>6,53; 11,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,1</t>
+          <t>6,01; 11,56</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,27</t>
+          <t>12,52; 16,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,02</t>
+          <t>10,8; 14,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,28</t>
+          <t>16,45; 19,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,27</t>
+          <t>12,52; 16,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,02</t>
+          <t>10,8; 14,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,28</t>
+          <t>16,45; 19,7</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84692</t>
+          <t>92856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84692</t>
+          <t>92856</t>
         </is>
       </c>
     </row>
@@ -1342,32 +1342,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37004; 59582</t>
+          <t>36324; 60122</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39178; 63505</t>
+          <t>38658; 63677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74176; 95088</t>
+          <t>81902; 105495</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37004; 59582</t>
+          <t>36324; 60122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39178; 63505</t>
+          <t>38658; 63677</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74176; 95088</t>
+          <t>81902; 105495</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59011</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59011</t>
+          <t>64622</t>
         </is>
       </c>
     </row>
@@ -1460,32 +1460,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33969; 58462</t>
+          <t>32913; 58257</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34228; 57860</t>
+          <t>34513; 58785</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49441; 69875</t>
+          <t>54133; 76044</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33969; 58462</t>
+          <t>32913; 58257</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34228; 57860</t>
+          <t>34513; 58785</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49441; 69875</t>
+          <t>54133; 76044</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12553</t>
         </is>
       </c>
     </row>
@@ -1578,32 +1578,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13887; 32553</t>
+          <t>13862; 31880</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6819; 19935</t>
+          <t>7818; 21285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7495; 17614</t>
+          <t>7800; 17866</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13887; 32553</t>
+          <t>13862; 31880</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6819; 19935</t>
+          <t>7818; 21285</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7495; 17614</t>
+          <t>7800; 17866</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>41113</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30016; 55880</t>
+          <t>30736; 55585</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21771; 44344</t>
+          <t>22402; 45450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11688; 69048</t>
+          <t>32264; 52192</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30016; 55880</t>
+          <t>30736; 55585</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21771; 44344</t>
+          <t>22402; 45450</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11688; 69048</t>
+          <t>32264; 52192</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>22142</t>
         </is>
       </c>
     </row>
@@ -1814,39 +1814,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22195; 45571</t>
+          <t>22275; 44825</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10595; 28473</t>
+          <t>11402; 29262</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12703; 29339</t>
+          <t>15107; 31465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22195; 45571</t>
+          <t>22275; 44825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10595; 28473</t>
+          <t>11402; 29262</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12703; 29339</t>
+          <t>15107; 31465</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>25728</t>
         </is>
       </c>
     </row>
@@ -1932,32 +1932,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32775; 59275</t>
+          <t>32343; 61886</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35344; 63521</t>
+          <t>35454; 64414</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17108; 31658</t>
+          <t>18459; 35524</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32775; 59275</t>
+          <t>32343; 61886</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35344; 63521</t>
+          <t>35454; 64414</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17108; 31658</t>
+          <t>18459; 35524</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235630</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>235630</t>
+          <t>259014</t>
         </is>
       </c>
     </row>
@@ -2050,32 +2050,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>205751; 265635</t>
+          <t>204437; 263225</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>181925; 236276</t>
+          <t>182022; 237421</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>150111; 283906</t>
+          <t>235725; 282346</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>205751; 265635</t>
+          <t>204437; 263225</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>181925; 236276</t>
+          <t>182022; 237421</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>150111; 283906</t>
+          <t>235725; 282346</t>
         </is>
       </c>
     </row>
